--- a/cert-data/Healthcare Certification Learning Report.xlsx
+++ b/cert-data/Healthcare Certification Learning Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konicaminoltanam-my.sharepoint.com/personal/rnesimi_kmbsus_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B877D12-820E-4081-8A24-016C13A192F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21F4B849-2699-417C-B849-765596645F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Dashboard Report" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="311">
   <si>
     <t>User</t>
   </si>
@@ -143,6 +143,9 @@
     <t>Healthcare Certification for Direct Sales</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Anna</t>
   </si>
   <si>
@@ -239,6 +242,18 @@
     <t>Jason.Ackerman@kmbs.konicaminolta.us</t>
   </si>
   <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>Chris</t>
+  </si>
+  <si>
+    <t>Curtis</t>
+  </si>
+  <si>
+    <t>ccurtis@kmbs.koniaminolta.us</t>
+  </si>
+  <si>
     <t>Gerri</t>
   </si>
   <si>
@@ -258,9 +273,6 @@
   </si>
   <si>
     <t>Daniel.Eldridge@kmbs.konicaminolta.us</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Philip</t>
@@ -2087,15 +2099,9 @@
       <c r="Q2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="5">
-        <v>46055</v>
-      </c>
-      <c r="S2" s="2" t="str">
-        <f>"FY"&amp;YEAR(R2)-IF(MONTH(R2)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R2),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2025 Q4</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>20</v>
+      <c r="R2" s="5"/>
+      <c r="T2" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="U2"/>
     </row>
@@ -2107,37 +2113,37 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N3" t="s">
         <v>32</v>
@@ -2151,15 +2157,9 @@
       <c r="Q3" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="5">
-        <v>46056</v>
-      </c>
-      <c r="S3" s="2" t="str">
-        <f>"FY"&amp;YEAR(R3)-IF(MONTH(R3)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R3),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2025 Q4</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>20</v>
+      <c r="R3" s="5"/>
+      <c r="T3" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="U3"/>
     </row>
@@ -2171,34 +2171,34 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
         <v>31</v>
@@ -2215,15 +2215,9 @@
       <c r="Q4" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="5">
-        <v>46057</v>
-      </c>
-      <c r="S4" s="2" t="str">
-        <f>"FY"&amp;YEAR(R4)-IF(MONTH(R4)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R4),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2025 Q4</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>20</v>
+      <c r="R4" s="5"/>
+      <c r="T4" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="U4"/>
     </row>
@@ -2235,37 +2229,37 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N5" t="s">
         <v>32</v>
@@ -2279,34 +2273,43 @@
       <c r="Q5" t="s">
         <v>34</v>
       </c>
-      <c r="R5" s="5">
-        <v>46137</v>
-      </c>
-      <c r="S5" s="2" t="str">
-        <f>"FY"&amp;YEAR(R5)-IF(MONTH(R5)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R5),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
-        <v>FY2026 Q1</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>20</v>
+      <c r="R5" s="5"/>
+      <c r="T5" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="B6" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="F6" t="s">
+        <v>68</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
       </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="O6" s="1">
         <v>46275</v>
       </c>
@@ -2314,9 +2317,9 @@
         <v>34</v>
       </c>
       <c r="R6" s="5">
-        <v>46203</v>
-      </c>
-      <c r="S6" s="2" t="str">
+        <v>46188</v>
+      </c>
+      <c r="S6" t="str">
         <f>"FY"&amp;YEAR(R6)-IF(MONTH(R6)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R6),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
         <v>FY2026 Q1</v>
       </c>
@@ -2333,37 +2336,37 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="M7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
         <v>32</v>
@@ -2379,7 +2382,7 @@
       </c>
       <c r="R7" s="2"/>
       <c r="T7" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U7"/>
     </row>
@@ -2391,37 +2394,37 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" t="s">
-        <v>70</v>
-      </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N8" t="s">
         <v>32</v>
@@ -2437,7 +2440,7 @@
       </c>
       <c r="R8" s="2"/>
       <c r="T8" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U8"/>
     </row>
@@ -2449,37 +2452,37 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
         <v>82</v>
       </c>
-      <c r="E9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" t="s">
-        <v>78</v>
-      </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N9" t="s">
         <v>32</v>
@@ -2495,7 +2498,7 @@
       </c>
       <c r="R9" s="2"/>
       <c r="T9" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U9"/>
     </row>
@@ -2507,37 +2510,37 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N10" t="s">
         <v>32</v>
@@ -2553,7 +2556,7 @@
       </c>
       <c r="R10" s="2"/>
       <c r="T10" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U10"/>
     </row>
@@ -2565,37 +2568,37 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L11" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N11" t="s">
         <v>32</v>
@@ -2611,7 +2614,7 @@
       </c>
       <c r="R11" s="2"/>
       <c r="T11" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U11"/>
     </row>
@@ -2623,37 +2626,37 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N12" t="s">
         <v>32</v>
@@ -2669,7 +2672,7 @@
       </c>
       <c r="R12" s="2"/>
       <c r="T12" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U12"/>
     </row>
@@ -2681,37 +2684,37 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M13" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N13" t="s">
         <v>32</v>
@@ -2727,7 +2730,7 @@
       </c>
       <c r="R13" s="2"/>
       <c r="T13" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U13"/>
     </row>
@@ -2739,37 +2742,37 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" t="s">
         <v>113</v>
       </c>
-      <c r="D14" t="s">
+      <c r="K14" t="s">
         <v>114</v>
       </c>
-      <c r="E14" t="s">
+      <c r="L14" t="s">
         <v>115</v>
       </c>
-      <c r="F14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="M14" t="s">
         <v>116</v>
-      </c>
-      <c r="J14" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" t="s">
-        <v>111</v>
-      </c>
-      <c r="M14" t="s">
-        <v>112</v>
       </c>
       <c r="N14" t="s">
         <v>32</v>
@@ -2785,7 +2788,7 @@
       </c>
       <c r="R14" s="2"/>
       <c r="T14" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U14"/>
     </row>
@@ -2797,37 +2800,37 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M15" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N15" t="s">
         <v>32</v>
@@ -2843,7 +2846,7 @@
       </c>
       <c r="R15" s="2"/>
       <c r="T15" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U15"/>
     </row>
@@ -2855,37 +2858,37 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M16" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N16" t="s">
         <v>32</v>
@@ -2901,7 +2904,7 @@
       </c>
       <c r="R16" s="2"/>
       <c r="T16" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U16"/>
     </row>
@@ -2913,34 +2916,34 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" t="s">
         <v>124</v>
       </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" t="s">
-        <v>120</v>
-      </c>
       <c r="I17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s">
         <v>31</v>
@@ -2959,7 +2962,7 @@
       </c>
       <c r="R17" s="2"/>
       <c r="T17" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U17"/>
     </row>
@@ -2971,37 +2974,37 @@
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I18" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J18" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N18" t="s">
         <v>32</v>
@@ -3017,7 +3020,7 @@
       </c>
       <c r="R18" s="2"/>
       <c r="T18" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U18"/>
     </row>
@@ -3029,37 +3032,37 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N19" t="s">
         <v>32</v>
@@ -3075,7 +3078,7 @@
       </c>
       <c r="R19" s="2"/>
       <c r="T19" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U19"/>
     </row>
@@ -3087,37 +3090,37 @@
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I20" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J20" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K20" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N20" t="s">
         <v>32</v>
@@ -3133,7 +3136,7 @@
       </c>
       <c r="R20" s="2"/>
       <c r="T20" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U20"/>
     </row>
@@ -3145,37 +3148,37 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I21" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J21" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L21" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N21" t="s">
         <v>32</v>
@@ -3191,7 +3194,7 @@
       </c>
       <c r="R21" s="2"/>
       <c r="T21" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U21"/>
     </row>
@@ -3203,37 +3206,37 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J22" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K22" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L22" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N22" t="s">
         <v>32</v>
@@ -3249,7 +3252,7 @@
       </c>
       <c r="R22" s="2"/>
       <c r="T22" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U22"/>
     </row>
@@ -3261,37 +3264,37 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I23" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J23" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K23" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L23" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N23" t="s">
         <v>32</v>
@@ -3307,7 +3310,7 @@
       </c>
       <c r="R23" s="2"/>
       <c r="T23" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U23"/>
     </row>
@@ -3319,37 +3322,37 @@
         <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E24" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N24" t="s">
         <v>32</v>
@@ -3365,7 +3368,7 @@
       </c>
       <c r="R24" s="2"/>
       <c r="T24" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U24"/>
     </row>
@@ -3377,13 +3380,13 @@
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F25" t="s">
         <v>24</v>
@@ -3392,22 +3395,22 @@
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I25" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J25" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K25" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N25" t="s">
         <v>32</v>
@@ -3423,7 +3426,7 @@
       </c>
       <c r="R25" s="2"/>
       <c r="T25" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U25"/>
     </row>
@@ -3435,16 +3438,16 @@
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
@@ -3453,7 +3456,7 @@
         <v>26</v>
       </c>
       <c r="I26" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J26" t="s">
         <v>28</v>
@@ -3481,7 +3484,7 @@
       </c>
       <c r="R26" s="2"/>
       <c r="T26" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U26"/>
     </row>
@@ -3493,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -3511,7 +3514,7 @@
         <v>26</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
         <v>28</v>
@@ -3539,7 +3542,7 @@
       </c>
       <c r="R27" s="2"/>
       <c r="T27" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U27"/>
     </row>
@@ -3551,16 +3554,16 @@
         <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D28" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E28" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F28" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
@@ -3569,7 +3572,7 @@
         <v>26</v>
       </c>
       <c r="I28" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J28" t="s">
         <v>28</v>
@@ -3597,7 +3600,7 @@
       </c>
       <c r="R28" s="2"/>
       <c r="T28" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U28"/>
     </row>
@@ -3609,13 +3612,13 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E29" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F29" t="s">
         <v>24</v>
@@ -3627,16 +3630,16 @@
         <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J29" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K29" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="M29" t="s">
         <v>31</v>
@@ -3655,7 +3658,7 @@
       </c>
       <c r="R29" s="2"/>
       <c r="T29" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U29"/>
     </row>
@@ -3667,37 +3670,37 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J30" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K30" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N30" t="s">
         <v>32</v>
@@ -3713,7 +3716,7 @@
       </c>
       <c r="R30" s="2"/>
       <c r="T30" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U30"/>
     </row>
@@ -3725,37 +3728,37 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
+        <v>194</v>
+      </c>
+      <c r="D31" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31" t="s">
+        <v>196</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" t="s">
         <v>190</v>
       </c>
-      <c r="D31" t="s">
+      <c r="I31" t="s">
+        <v>190</v>
+      </c>
+      <c r="J31" t="s">
         <v>191</v>
       </c>
-      <c r="E31" t="s">
+      <c r="K31" t="s">
         <v>192</v>
       </c>
-      <c r="F31" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" t="s">
-        <v>49</v>
-      </c>
-      <c r="H31" t="s">
-        <v>186</v>
-      </c>
-      <c r="I31" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" t="s">
-        <v>187</v>
-      </c>
-      <c r="K31" t="s">
-        <v>188</v>
-      </c>
       <c r="L31" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -3771,7 +3774,7 @@
       </c>
       <c r="R31" s="2"/>
       <c r="T31" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U31"/>
     </row>
@@ -3783,37 +3786,37 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" t="s">
+        <v>190</v>
+      </c>
+      <c r="I32" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" t="s">
+        <v>192</v>
+      </c>
+      <c r="L32" t="s">
         <v>193</v>
       </c>
-      <c r="E32" t="s">
-        <v>194</v>
-      </c>
-      <c r="F32" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" t="s">
-        <v>49</v>
-      </c>
-      <c r="H32" t="s">
-        <v>186</v>
-      </c>
-      <c r="I32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K32" t="s">
-        <v>188</v>
-      </c>
-      <c r="L32" t="s">
-        <v>189</v>
-      </c>
       <c r="M32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N32" t="s">
         <v>32</v>
@@ -3829,7 +3832,7 @@
       </c>
       <c r="R32" s="2"/>
       <c r="T32" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U32"/>
     </row>
@@ -3841,13 +3844,13 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
         <v>24</v>
@@ -3856,19 +3859,19 @@
         <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I33" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J33" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K33" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L33" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M33" t="s">
         <v>31</v>
@@ -3887,7 +3890,7 @@
       </c>
       <c r="R33" s="2"/>
       <c r="T33" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U33"/>
     </row>
@@ -3899,37 +3902,37 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E34" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I34" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J34" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K34" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="L34" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N34" t="s">
         <v>32</v>
@@ -3945,7 +3948,7 @@
       </c>
       <c r="R34" s="2"/>
       <c r="T34" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U34"/>
     </row>
@@ -3957,37 +3960,37 @@
         <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D35" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E35" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F35" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I35" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J35" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K35" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L35" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N35" t="s">
         <v>32</v>
@@ -4003,7 +4006,7 @@
       </c>
       <c r="R35" s="2"/>
       <c r="T35" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U35"/>
     </row>
@@ -4015,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D36" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E36" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
         <v>24</v>
@@ -4030,19 +4033,19 @@
         <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I36" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J36" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K36" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M36" t="s">
         <v>31</v>
@@ -4061,7 +4064,7 @@
       </c>
       <c r="R36" s="2"/>
       <c r="T36" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U36"/>
     </row>
@@ -4073,37 +4076,37 @@
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D37" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J37" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K37" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="L37" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N37" t="s">
         <v>32</v>
@@ -4119,7 +4122,7 @@
       </c>
       <c r="R37" s="2"/>
       <c r="T37" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U37"/>
     </row>
@@ -4131,34 +4134,34 @@
         <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J38" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K38" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L38" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M38" t="s">
         <v>31</v>
@@ -4177,7 +4180,7 @@
       </c>
       <c r="R38" s="2"/>
       <c r="T38" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U38"/>
     </row>
@@ -4189,34 +4192,34 @@
         <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E39" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F39" t="s">
         <v>24</v>
       </c>
       <c r="G39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M39" t="s">
         <v>31</v>
@@ -4235,7 +4238,7 @@
       </c>
       <c r="R39" s="2"/>
       <c r="T39" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U39"/>
     </row>
@@ -4247,34 +4250,34 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D40" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E40" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F40" t="s">
         <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M40" t="s">
         <v>31</v>
@@ -4293,7 +4296,7 @@
       </c>
       <c r="R40" s="2"/>
       <c r="T40" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U40"/>
     </row>
@@ -4305,37 +4308,37 @@
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J41" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K41" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L41" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="M41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N41" t="s">
         <v>32</v>
@@ -4351,7 +4354,7 @@
       </c>
       <c r="R41" s="2"/>
       <c r="T41" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U41"/>
     </row>
@@ -4363,37 +4366,37 @@
         <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K42" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="L42" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="M42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N42" t="s">
         <v>32</v>
@@ -4409,7 +4412,7 @@
       </c>
       <c r="R42" s="2"/>
       <c r="T42" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U42"/>
     </row>
@@ -4421,43 +4424,43 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H43" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J43" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K43" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L43" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M43" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N43" t="s">
         <v>32</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="P43" t="s">
         <v>33</v>
@@ -4467,7 +4470,7 @@
       </c>
       <c r="R43" s="2"/>
       <c r="T43" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U43"/>
     </row>
@@ -4479,43 +4482,43 @@
         <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F44" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J44" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K44" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L44" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M44" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N44" t="s">
         <v>32</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="P44" t="s">
         <v>33</v>
@@ -4525,7 +4528,7 @@
       </c>
       <c r="R44" s="2"/>
       <c r="T44" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U44"/>
     </row>
@@ -4537,43 +4540,43 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H45" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K45" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L45" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N45" t="s">
         <v>32</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="P45" t="s">
         <v>33</v>
@@ -4583,7 +4586,7 @@
       </c>
       <c r="R45" s="2"/>
       <c r="T45" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U45"/>
     </row>
@@ -4595,43 +4598,43 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H46" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I46" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K46" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="L46" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="M46" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="N46" t="s">
         <v>32</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P46" t="s">
         <v>33</v>
@@ -4641,7 +4644,7 @@
       </c>
       <c r="R46" s="2"/>
       <c r="T46" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U46"/>
     </row>
@@ -4653,43 +4656,43 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H47" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J47" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K47" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L47" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M47" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N47" t="s">
         <v>32</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="P47" t="s">
         <v>33</v>
@@ -4699,7 +4702,7 @@
       </c>
       <c r="R47" s="2"/>
       <c r="T47" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U47"/>
     </row>
@@ -4711,43 +4714,43 @@
         <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F48" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H48" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I48" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J48" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K48" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L48" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M48" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N48" t="s">
         <v>32</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="P48" t="s">
         <v>33</v>
@@ -4757,7 +4760,7 @@
       </c>
       <c r="R48" s="2"/>
       <c r="T48" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U48"/>
     </row>
@@ -4769,43 +4772,43 @@
         <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F49" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J49" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K49" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="L49" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M49" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N49" t="s">
         <v>32</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="P49" t="s">
         <v>33</v>
@@ -4815,7 +4818,7 @@
       </c>
       <c r="R49" s="2"/>
       <c r="T49" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U49"/>
     </row>
@@ -4827,43 +4830,43 @@
         <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E50" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F50" t="s">
         <v>31</v>
       </c>
       <c r="G50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H50" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I50" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J50" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K50" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L50" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N50" t="s">
         <v>32</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="P50" t="s">
         <v>33</v>
@@ -4873,7 +4876,7 @@
       </c>
       <c r="R50" s="2"/>
       <c r="T50" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U50"/>
     </row>
@@ -4885,43 +4888,43 @@
         <v>20</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I51" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J51" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L51" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M51" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N51" t="s">
         <v>32</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P51" t="s">
         <v>33</v>
@@ -4931,7 +4934,7 @@
       </c>
       <c r="R51" s="2"/>
       <c r="T51" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U51"/>
     </row>
@@ -4943,43 +4946,43 @@
         <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D52" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H52" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I52" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J52" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K52" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L52" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M52" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N52" t="s">
         <v>32</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="P52" t="s">
         <v>33</v>
@@ -4989,7 +4992,7 @@
       </c>
       <c r="R52" s="2"/>
       <c r="T52" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U52"/>
     </row>
@@ -5013,31 +5016,31 @@
         <v>31</v>
       </c>
       <c r="G53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H53" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I53" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J53" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K53" t="s">
         <v>29</v>
       </c>
       <c r="L53" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="M53" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N53" t="s">
         <v>32</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="P53" t="s">
         <v>33</v>
@@ -5047,7 +5050,7 @@
       </c>
       <c r="R53" s="2"/>
       <c r="T53" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U53"/>
     </row>
@@ -5059,43 +5062,43 @@
         <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D54" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F54" t="s">
         <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I54" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J54" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K54" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="L54" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="M54" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="N54" t="s">
         <v>32</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="P54" t="s">
         <v>33</v>
@@ -5105,7 +5108,7 @@
       </c>
       <c r="R54" s="2"/>
       <c r="T54" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U54"/>
     </row>
@@ -5117,43 +5120,43 @@
         <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D55" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E55" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K55" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="L55" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M55" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N55" t="s">
         <v>32</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="P55" t="s">
         <v>33</v>
@@ -5163,7 +5166,7 @@
       </c>
       <c r="R55" s="2"/>
       <c r="T55" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U55"/>
     </row>
@@ -5175,43 +5178,43 @@
         <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D56" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E56" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F56" t="s">
         <v>31</v>
       </c>
       <c r="G56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H56" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I56" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J56" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K56" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L56" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M56" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="N56" t="s">
         <v>32</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P56" t="s">
         <v>33</v>
@@ -5221,7 +5224,7 @@
       </c>
       <c r="R56" s="2"/>
       <c r="T56" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U56"/>
     </row>
@@ -5233,43 +5236,43 @@
         <v>20</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D57" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E57" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H57" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I57" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J57" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K57" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="L57" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="M57" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N57" t="s">
         <v>32</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P57" t="s">
         <v>33</v>
@@ -5279,7 +5282,7 @@
       </c>
       <c r="R57" s="2"/>
       <c r="T57" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U57"/>
     </row>
@@ -5291,43 +5294,43 @@
         <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D58" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E58" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H58" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I58" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J58" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K58" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="L58" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="M58" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N58" t="s">
         <v>32</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="P58" t="s">
         <v>33</v>
@@ -5337,7 +5340,7 @@
       </c>
       <c r="R58" s="2"/>
       <c r="T58" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U58"/>
     </row>
@@ -5349,43 +5352,43 @@
         <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F59" t="s">
         <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J59" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K59" t="s">
         <v>29</v>
       </c>
       <c r="L59" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M59" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N59" t="s">
         <v>32</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="P59" t="s">
         <v>33</v>
@@ -5395,7 +5398,7 @@
       </c>
       <c r="R59" s="2"/>
       <c r="T59" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U59"/>
     </row>
@@ -5407,43 +5410,43 @@
         <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D60" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E60" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J60" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K60" t="s">
         <v>29</v>
       </c>
       <c r="L60" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M60" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N60" t="s">
         <v>32</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="P60" t="s">
         <v>33</v>
@@ -5453,7 +5456,7 @@
       </c>
       <c r="R60" s="2"/>
       <c r="T60" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U60"/>
     </row>
@@ -5465,43 +5468,43 @@
         <v>20</v>
       </c>
       <c r="C61" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D61" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E61" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J61" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K61" t="s">
         <v>29</v>
       </c>
       <c r="L61" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M61" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N61" t="s">
         <v>32</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P61" t="s">
         <v>33</v>
@@ -5511,29 +5514,32 @@
       </c>
       <c r="R61" s="2"/>
       <c r="T61" s="10" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="U61"/>
     </row>
     <row r="62" spans="1:21">
       <c r="C62" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D62" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F62" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G62" t="s">
         <v>25</v>
       </c>
+      <c r="H62" t="s">
+        <v>51</v>
+      </c>
       <c r="R62" s="2"/>
       <c r="T62" s="10" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -5546,10 +5552,11 @@
   <hyperlinks>
     <hyperlink ref="E62" r:id="rId1" xr:uid="{7B1C40F8-03EF-4CB2-8FAB-7B0A1F53AFC7}"/>
     <hyperlink ref="E6" r:id="rId2" xr:uid="{02D73FA1-C748-4DD6-82AA-1A7FD33A6BBA}"/>
+    <hyperlink ref="L6" r:id="rId3" xr:uid="{6E695026-1CD2-4AA5-9B44-E9810C2C0E1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>